--- a/src/main/java/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="96">
   <si>
     <t>RFC</t>
   </si>
@@ -309,6 +309,21 @@
   </si>
   <si>
     <t>Transferencia Electronica Fondos</t>
+  </si>
+  <si>
+    <t>prue01</t>
+  </si>
+  <si>
+    <t>PRUEBA</t>
+  </si>
+  <si>
+    <t>PRU230326XXRRFS</t>
+  </si>
+  <si>
+    <t>CONTADO</t>
+  </si>
+  <si>
+    <t>5578901234</t>
   </si>
 </sst>
 </file>
@@ -692,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2328CBE3-6A92-456E-9134-BFBEA6F1CED4}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="13.7265625" collapsed="true"/>
@@ -947,8 +962,8 @@
       <c r="C9" t="s">
         <v>52</v>
       </c>
-      <c r="D9">
-        <v>5578901234</v>
+      <c r="D9" t="s">
+        <v>95</v>
       </c>
       <c r="E9" t="s">
         <v>53</v>
@@ -961,6 +976,18 @@
       </c>
       <c r="H9">
         <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" t="s">
+        <v>89</v>
+      </c>
+      <c r="K9" t="s">
+        <v>90</v>
+      </c>
+      <c r="L9" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -1065,6 +1092,44 @@
       </c>
       <c r="H13">
         <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14" t="s">
+        <v>89</v>
+      </c>
+      <c r="K14" t="s">
+        <v>90</v>
+      </c>
+      <c r="L14" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="96">
   <si>
     <t>RFC</t>
   </si>
@@ -847,6 +847,9 @@
       <c r="H4">
         <v>1</v>
       </c>
+      <c r="L4" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">

--- a/src/main/java/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="96">
   <si>
     <t>RFC</t>
   </si>

--- a/src/main/java/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591514D5-92A4-4950-928E-91B40A3ACFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5E48F9-E218-436F-96D2-35884583FCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EBE529F0-1989-4E0B-B87D-8E5A162CA571}"/>
+    <workbookView xWindow="3024" yWindow="2304" windowWidth="16740" windowHeight="9372" xr2:uid="{EBE529F0-1989-4E0B-B87D-8E5A162CA571}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="94">
   <si>
     <t>RFC</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Avenida Eje 5 Sur No. 149 Col. Chinampac De Juarez, Iztapalapa, Iztapalapa, Ciudad de México C.P. 09208</t>
   </si>
   <si>
-    <t>SHEILA</t>
-  </si>
-  <si>
     <t>BIMBO S.A. DE C.V.</t>
   </si>
   <si>
@@ -288,9 +285,6 @@
   </si>
   <si>
     <t>FORMA_PAGO</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>1</t>
@@ -330,8 +324,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -343,6 +336,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -708,24 +707,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2328CBE3-6A92-456E-9134-BFBEA6F1CED4}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="13.7265625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="28.6328125" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="16.7265625" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="10.81640625" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="25.453125" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="86.36328125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="9.90625" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="7.0" collapsed="true"/>
+    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="25.44140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="86.33203125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="15.21875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
         <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -743,33 +742,33 @@
         <v>3</v>
       </c>
       <c r="H1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" t="s">
         <v>80</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>81</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>82</v>
       </c>
-      <c r="K1" t="s">
-        <v>83</v>
-      </c>
       <c r="L1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
@@ -778,337 +777,454 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J2" t="s">
         <v>87</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>88</v>
       </c>
-      <c r="J2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" t="s">
-        <v>90</v>
-      </c>
       <c r="L2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
       </c>
       <c r="D3">
         <v>5512345678</v>
       </c>
       <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K3" t="s">
+        <v>88</v>
+      </c>
+      <c r="L3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
       </c>
       <c r="D4">
         <v>5523456789</v>
       </c>
       <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>24</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K4" t="s">
+        <v>88</v>
+      </c>
+      <c r="L4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>25</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
       </c>
       <c r="D5">
         <v>5534567890</v>
       </c>
       <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>31</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
       </c>
       <c r="D6">
         <v>5545678901</v>
       </c>
       <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
         <v>35</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>36</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I6" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>37</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>38</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>39</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
       </c>
       <c r="D7">
         <v>5556789012</v>
       </c>
       <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
         <v>41</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>42</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
+        <v>92</v>
+      </c>
+      <c r="I7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" t="s">
+        <v>87</v>
+      </c>
+      <c r="K7" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>43</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>44</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>45</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
       </c>
       <c r="D8">
         <v>5567890123</v>
       </c>
       <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
         <v>47</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>48</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>49</v>
       </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>50</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>51</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" t="s">
         <v>52</v>
       </c>
-      <c r="D9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>53</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>54</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
+        <v>92</v>
+      </c>
+      <c r="I9" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>55</v>
       </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" t="s">
-        <v>89</v>
-      </c>
-      <c r="K9" t="s">
-        <v>90</v>
-      </c>
-      <c r="L9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>56</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>57</v>
-      </c>
-      <c r="C10" t="s">
-        <v>58</v>
       </c>
       <c r="D10">
         <v>5589012345</v>
       </c>
       <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
         <v>59</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>60</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I10" t="s">
+        <v>86</v>
+      </c>
+      <c r="J10" t="s">
+        <v>87</v>
+      </c>
+      <c r="K10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>61</v>
       </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>62</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>64</v>
       </c>
       <c r="D11">
         <v>5590123456</v>
       </c>
       <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
         <v>65</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>66</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
+        <v>92</v>
+      </c>
+      <c r="I11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>67</v>
       </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>68</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
       </c>
       <c r="D12">
         <v>5511122233</v>
       </c>
       <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
         <v>71</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>72</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I12" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" t="s">
+        <v>87</v>
+      </c>
+      <c r="K12" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>73</v>
       </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>74</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>76</v>
       </c>
       <c r="D13">
         <v>5555555555</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" t="s">
         <v>77</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>78</v>
       </c>
-      <c r="G13" t="s">
-        <v>79</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="H13" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" t="s">
+        <v>86</v>
+      </c>
+      <c r="J13" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" t="s">
+        <v>88</v>
+      </c>
+      <c r="L13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" t="s">
         <v>91</v>
       </c>
-      <c r="B14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" t="s">
-        <v>93</v>
-      </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -1117,25 +1233,26 @@
         <v>8</v>
       </c>
       <c r="G14" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" t="s">
+        <v>92</v>
+      </c>
+      <c r="I14" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" t="s">
         <v>87</v>
       </c>
-      <c r="H14" t="s">
-        <v>94</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
         <v>88</v>
       </c>
-      <c r="J14" t="s">
-        <v>89</v>
-      </c>
-      <c r="K14" t="s">
-        <v>90</v>
-      </c>
       <c r="L14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{9E8DA580-04F7-4207-BBF7-CACE85CDF085}"/>
     <hyperlink ref="E13" r:id="rId2" xr:uid="{BEBA4C49-389C-4DDF-BA14-30964A46AE44}"/>

--- a/src/main/java/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5E48F9-E218-436F-96D2-35884583FCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6904205-36F3-45BC-83A5-2DCA2CEEEA5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3024" yWindow="2304" windowWidth="16740" windowHeight="9372" xr2:uid="{EBE529F0-1989-4E0B-B87D-8E5A162CA571}"/>
+    <workbookView xWindow="612" yWindow="-108" windowWidth="22536" windowHeight="13176" xr2:uid="{EBE529F0-1989-4E0B-B87D-8E5A162CA571}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -716,7 +716,10 @@
     <col min="5" max="5" width="25.44140625" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="6" max="6" width="86.33203125" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="15.21875" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="9.44140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="33" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
